--- a/reports/Analisis_Metas_Kelder.xlsx
+++ b/reports/Analisis_Metas_Kelder.xlsx
@@ -1472,7 +1472,7 @@
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="36" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>➡️ Estable</t>
+          <t>⚠️ Sin datos recientes</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>➡️ Estable</t>
+          <t>🆕 Sucursal nueva</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>➡️ Estable</t>
+          <t>⚠️ Sin datos recientes</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
